--- a/templates/eip_annual_map_template.xlsx
+++ b/templates/eip_annual_map_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5415AEBF-A43C-4264-8966-E3DEC3315F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BA617D-6FFB-4E5A-8115-7E69FDF2D481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C9518E58-1CD8-4B80-8CC5-091D741A5E47}"/>
   </bookViews>
@@ -127,7 +127,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -285,11 +285,147 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -318,11 +454,47 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -352,7 +524,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>499500</xdr:colOff>
+      <xdr:colOff>171450</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>138000</xdr:rowOff>
     </xdr:to>
@@ -384,7 +556,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="190500" y="190500"/>
-          <a:ext cx="4500000" cy="900000"/>
+          <a:ext cx="4171950" cy="900000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -693,7 +865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742F823C-5441-447F-AAA4-969ED94BF308}">
-  <dimension ref="B7:AL42"/>
+  <dimension ref="A7:AL42"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
@@ -738,148 +910,148 @@
   </cols>
   <sheetData>
     <row r="7" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="13"/>
-      <c r="AG7" s="13"/>
-      <c r="AH7" s="13"/>
-      <c r="AI7" s="13"/>
-      <c r="AJ7" s="13"/>
-      <c r="AK7" s="13"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="12"/>
+      <c r="AB7" s="12"/>
+      <c r="AC7" s="12"/>
+      <c r="AD7" s="12"/>
+      <c r="AE7" s="12"/>
+      <c r="AF7" s="12"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
+      <c r="AJ7" s="12"/>
+      <c r="AK7" s="12"/>
     </row>
     <row r="8" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="13"/>
-      <c r="AA8" s="13"/>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="13"/>
-      <c r="AD8" s="13"/>
-      <c r="AE8" s="13"/>
-      <c r="AF8" s="13"/>
-      <c r="AG8" s="13"/>
-      <c r="AH8" s="13"/>
-      <c r="AI8" s="13"/>
-      <c r="AJ8" s="13"/>
-      <c r="AK8" s="13"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="12"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="12"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="12"/>
+      <c r="AA8" s="12"/>
+      <c r="AB8" s="12"/>
+      <c r="AC8" s="12"/>
+      <c r="AD8" s="12"/>
+      <c r="AE8" s="12"/>
+      <c r="AF8" s="12"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="12"/>
+      <c r="AI8" s="12"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
     </row>
     <row r="10" spans="2:37" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12" t="s">
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12" t="s">
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12" t="s">
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12" t="s">
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12" t="s">
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="U10" s="12"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="12" t="s">
+      <c r="U10" s="13"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="X10" s="12"/>
-      <c r="Y10" s="12"/>
-      <c r="Z10" s="12" t="s">
+      <c r="X10" s="13"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AA10" s="12"/>
-      <c r="AB10" s="12"/>
-      <c r="AC10" s="12" t="s">
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="13"/>
+      <c r="AC10" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AD10" s="12"/>
-      <c r="AE10" s="12"/>
-      <c r="AF10" s="12" t="s">
+      <c r="AD10" s="13"/>
+      <c r="AE10" s="13"/>
+      <c r="AF10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AG10" s="12"/>
-      <c r="AH10" s="12"/>
-      <c r="AI10" s="12" t="s">
+      <c r="AG10" s="13"/>
+      <c r="AH10" s="13"/>
+      <c r="AI10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="AJ10" s="12"/>
-      <c r="AK10" s="12"/>
+      <c r="AJ10" s="13"/>
+      <c r="AK10" s="13"/>
     </row>
     <row r="11" spans="2:37" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
       <c r="C11" s="2"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="10"/>
+      <c r="E11" s="1"/>
       <c r="F11" s="2"/>
       <c r="G11" s="3"/>
       <c r="H11" s="10"/>
@@ -917,7 +1089,7 @@
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
       <c r="D12" s="6"/>
-      <c r="E12" s="11"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="5"/>
       <c r="G12" s="6"/>
       <c r="H12" s="11"/>
@@ -955,7 +1127,7 @@
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="11"/>
+      <c r="E13" s="4"/>
       <c r="F13" s="5"/>
       <c r="G13" s="6"/>
       <c r="H13" s="11"/>
@@ -993,7 +1165,7 @@
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
       <c r="D14" s="6"/>
-      <c r="E14" s="11"/>
+      <c r="E14" s="4"/>
       <c r="F14" s="5"/>
       <c r="G14" s="6"/>
       <c r="H14" s="11"/>
@@ -1031,7 +1203,7 @@
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="11"/>
+      <c r="E15" s="4"/>
       <c r="F15" s="5"/>
       <c r="G15" s="6"/>
       <c r="H15" s="11"/>
@@ -1069,7 +1241,7 @@
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="6"/>
-      <c r="E16" s="11"/>
+      <c r="E16" s="4"/>
       <c r="F16" s="5"/>
       <c r="G16" s="6"/>
       <c r="H16" s="11"/>
@@ -1107,7 +1279,7 @@
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="6"/>
-      <c r="E17" s="11"/>
+      <c r="E17" s="4"/>
       <c r="F17" s="5"/>
       <c r="G17" s="6"/>
       <c r="H17" s="11"/>
@@ -1145,7 +1317,7 @@
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="6"/>
-      <c r="E18" s="11"/>
+      <c r="E18" s="4"/>
       <c r="F18" s="5"/>
       <c r="G18" s="6"/>
       <c r="H18" s="11"/>
@@ -1183,7 +1355,7 @@
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
       <c r="D19" s="6"/>
-      <c r="E19" s="11"/>
+      <c r="E19" s="4"/>
       <c r="F19" s="5"/>
       <c r="G19" s="6"/>
       <c r="H19" s="11"/>
@@ -1221,7 +1393,7 @@
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
       <c r="D20" s="6"/>
-      <c r="E20" s="11"/>
+      <c r="E20" s="4"/>
       <c r="F20" s="5"/>
       <c r="G20" s="6"/>
       <c r="H20" s="11"/>
@@ -1259,7 +1431,7 @@
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
       <c r="D21" s="6"/>
-      <c r="E21" s="11"/>
+      <c r="E21" s="4"/>
       <c r="F21" s="5"/>
       <c r="G21" s="6"/>
       <c r="H21" s="11"/>
@@ -1297,7 +1469,7 @@
       <c r="B22" s="4"/>
       <c r="C22" s="5"/>
       <c r="D22" s="6"/>
-      <c r="E22" s="11"/>
+      <c r="E22" s="4"/>
       <c r="F22" s="5"/>
       <c r="G22" s="6"/>
       <c r="H22" s="11"/>
@@ -1335,7 +1507,7 @@
       <c r="B23" s="4"/>
       <c r="C23" s="5"/>
       <c r="D23" s="6"/>
-      <c r="E23" s="11"/>
+      <c r="E23" s="4"/>
       <c r="F23" s="5"/>
       <c r="G23" s="6"/>
       <c r="H23" s="11"/>
@@ -1373,7 +1545,7 @@
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="11"/>
+      <c r="E24" s="4"/>
       <c r="F24" s="5"/>
       <c r="G24" s="6"/>
       <c r="H24" s="11"/>
@@ -1411,7 +1583,7 @@
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
       <c r="D25" s="6"/>
-      <c r="E25" s="11"/>
+      <c r="E25" s="4"/>
       <c r="F25" s="5"/>
       <c r="G25" s="6"/>
       <c r="H25" s="11"/>
@@ -1449,7 +1621,7 @@
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
       <c r="D26" s="6"/>
-      <c r="E26" s="11"/>
+      <c r="E26" s="4"/>
       <c r="F26" s="5"/>
       <c r="G26" s="6"/>
       <c r="H26" s="11"/>
@@ -1487,7 +1659,7 @@
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
       <c r="D27" s="6"/>
-      <c r="E27" s="11"/>
+      <c r="E27" s="4"/>
       <c r="F27" s="5"/>
       <c r="G27" s="6"/>
       <c r="H27" s="11"/>
@@ -1525,7 +1697,7 @@
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
       <c r="D28" s="6"/>
-      <c r="E28" s="11"/>
+      <c r="E28" s="4"/>
       <c r="F28" s="5"/>
       <c r="G28" s="6"/>
       <c r="H28" s="11"/>
@@ -1563,7 +1735,7 @@
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
       <c r="D29" s="6"/>
-      <c r="E29" s="11"/>
+      <c r="E29" s="4"/>
       <c r="F29" s="5"/>
       <c r="G29" s="6"/>
       <c r="H29" s="11"/>
@@ -1601,7 +1773,7 @@
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
       <c r="D30" s="6"/>
-      <c r="E30" s="11"/>
+      <c r="E30" s="4"/>
       <c r="F30" s="5"/>
       <c r="G30" s="6"/>
       <c r="H30" s="11"/>
@@ -1639,7 +1811,7 @@
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
       <c r="D31" s="6"/>
-      <c r="E31" s="11"/>
+      <c r="E31" s="4"/>
       <c r="F31" s="5"/>
       <c r="G31" s="6"/>
       <c r="H31" s="11"/>
@@ -1677,7 +1849,7 @@
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
       <c r="D32" s="6"/>
-      <c r="E32" s="11"/>
+      <c r="E32" s="4"/>
       <c r="F32" s="5"/>
       <c r="G32" s="6"/>
       <c r="H32" s="11"/>
@@ -1715,7 +1887,7 @@
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
       <c r="D33" s="6"/>
-      <c r="E33" s="11"/>
+      <c r="E33" s="4"/>
       <c r="F33" s="5"/>
       <c r="G33" s="6"/>
       <c r="H33" s="11"/>
@@ -1753,7 +1925,7 @@
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
       <c r="D34" s="6"/>
-      <c r="E34" s="11"/>
+      <c r="E34" s="4"/>
       <c r="F34" s="5"/>
       <c r="G34" s="6"/>
       <c r="H34" s="11"/>
@@ -1791,7 +1963,7 @@
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
       <c r="D35" s="6"/>
-      <c r="E35" s="11"/>
+      <c r="E35" s="4"/>
       <c r="F35" s="5"/>
       <c r="G35" s="6"/>
       <c r="H35" s="11"/>
@@ -1829,7 +2001,7 @@
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="6"/>
-      <c r="E36" s="11"/>
+      <c r="E36" s="4"/>
       <c r="F36" s="5"/>
       <c r="G36" s="6"/>
       <c r="H36" s="11"/>
@@ -1867,7 +2039,7 @@
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
       <c r="D37" s="6"/>
-      <c r="E37" s="11"/>
+      <c r="E37" s="4"/>
       <c r="F37" s="5"/>
       <c r="G37" s="6"/>
       <c r="H37" s="11"/>
@@ -1905,7 +2077,7 @@
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
       <c r="D38" s="6"/>
-      <c r="E38" s="11"/>
+      <c r="E38" s="4"/>
       <c r="F38" s="5"/>
       <c r="G38" s="6"/>
       <c r="H38" s="11"/>
@@ -1943,7 +2115,7 @@
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
       <c r="D39" s="6"/>
-      <c r="E39" s="11"/>
+      <c r="E39" s="4"/>
       <c r="F39" s="5"/>
       <c r="G39" s="6"/>
       <c r="H39" s="11"/>
@@ -1981,9 +2153,9 @@
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
       <c r="D40" s="6"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="6"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="16"/>
       <c r="H40" s="11"/>
       <c r="I40" s="5"/>
       <c r="J40" s="6"/>
@@ -2016,83 +2188,89 @@
       <c r="AK40" s="6"/>
     </row>
     <row r="41" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B41" s="4"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="6"/>
-      <c r="Q41" s="11"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="6"/>
-      <c r="T41" s="11"/>
-      <c r="U41" s="5"/>
-      <c r="V41" s="6"/>
-      <c r="W41" s="11"/>
-      <c r="X41" s="5"/>
-      <c r="Y41" s="6"/>
-      <c r="Z41" s="11"/>
-      <c r="AA41" s="5"/>
-      <c r="AB41" s="6"/>
-      <c r="AC41" s="11"/>
-      <c r="AD41" s="5"/>
-      <c r="AE41" s="6"/>
-      <c r="AF41" s="11"/>
-      <c r="AG41" s="5"/>
-      <c r="AH41" s="6"/>
-      <c r="AI41" s="11"/>
-      <c r="AJ41" s="5"/>
-      <c r="AK41" s="6"/>
-    </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.25">
-      <c r="B42" s="7"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="8"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="7"/>
-      <c r="O42" s="8"/>
-      <c r="P42" s="9"/>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="9"/>
-      <c r="T42" s="7"/>
-      <c r="U42" s="8"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="7"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="7"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="7"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="9"/>
-      <c r="AF42" s="7"/>
-      <c r="AG42" s="8"/>
-      <c r="AH42" s="9"/>
-      <c r="AI42" s="7"/>
-      <c r="AJ42" s="8"/>
-      <c r="AK42" s="9"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="21"/>
+      <c r="M41" s="22"/>
+      <c r="N41" s="7"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="21"/>
+      <c r="S41" s="22"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="8"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="7"/>
+      <c r="X41" s="8"/>
+      <c r="Y41" s="9"/>
+      <c r="Z41" s="20"/>
+      <c r="AA41" s="21"/>
+      <c r="AB41" s="22"/>
+      <c r="AC41" s="7"/>
+      <c r="AD41" s="8"/>
+      <c r="AE41" s="9"/>
+      <c r="AF41" s="20"/>
+      <c r="AG41" s="21"/>
+      <c r="AH41" s="22"/>
+      <c r="AI41" s="7"/>
+      <c r="AJ41" s="8"/>
+      <c r="AK41" s="9"/>
+    </row>
+    <row r="42" spans="2:37" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="23"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
+      <c r="R42" s="24"/>
+      <c r="S42" s="24"/>
+      <c r="T42" s="24"/>
+      <c r="U42" s="24"/>
+      <c r="V42" s="24"/>
+      <c r="W42" s="24"/>
+      <c r="X42" s="24"/>
+      <c r="Y42" s="24"/>
+      <c r="Z42" s="24"/>
+      <c r="AA42" s="24"/>
+      <c r="AB42" s="24"/>
+      <c r="AC42" s="24"/>
+      <c r="AD42" s="24"/>
+      <c r="AE42" s="24"/>
+      <c r="AF42" s="24"/>
+      <c r="AG42" s="24"/>
+      <c r="AH42" s="24"/>
+      <c r="AI42" s="24"/>
+      <c r="AJ42" s="24"/>
+      <c r="AK42" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="19">
+    <mergeCell ref="B42:AK42"/>
+    <mergeCell ref="E40:G41"/>
+    <mergeCell ref="K41:M41"/>
+    <mergeCell ref="AF41:AH41"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Q41:S41"/>
     <mergeCell ref="B7:AK8"/>
     <mergeCell ref="T10:V10"/>
     <mergeCell ref="W10:Y10"/>

--- a/templates/eip_annual_map_template.xlsx
+++ b/templates/eip_annual_map_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BA617D-6FFB-4E5A-8115-7E69FDF2D481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC77669B-6C3B-4269-9CE1-151EBEB2B8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C9518E58-1CD8-4B80-8CC5-091D741A5E47}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>JANEIRO</t>
   </si>
@@ -71,12 +71,18 @@
   <si>
     <t>DEZEMBRO</t>
   </si>
+  <si>
+    <t>O Comandante</t>
+  </si>
+  <si>
+    <t>Jorge Carmo</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,6 +118,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -127,7 +140,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -421,11 +434,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -495,6 +517,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -865,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{742F823C-5441-447F-AAA4-969ED94BF308}">
-  <dimension ref="A7:AL42"/>
+  <dimension ref="A7:AL52"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
@@ -2263,9 +2291,59 @@
       <c r="AJ42" s="24"/>
       <c r="AK42" s="25"/>
     </row>
+    <row r="43" spans="2:37" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="2:37" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="Q48" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="R48" s="26"/>
+      <c r="S48" s="26"/>
+      <c r="T48" s="26"/>
+      <c r="U48" s="26"/>
+      <c r="V48" s="26"/>
+    </row>
+    <row r="49" spans="17:22" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="Q49" s="26"/>
+      <c r="R49" s="26"/>
+      <c r="S49" s="26"/>
+      <c r="T49" s="26"/>
+      <c r="U49" s="26"/>
+      <c r="V49" s="26"/>
+    </row>
+    <row r="50" spans="17:22" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="Q50" s="26"/>
+      <c r="R50" s="26"/>
+      <c r="S50" s="26"/>
+      <c r="T50" s="26"/>
+      <c r="U50" s="26"/>
+      <c r="V50" s="26"/>
+    </row>
+    <row r="51" spans="17:22" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="Q51" s="27"/>
+      <c r="R51" s="27"/>
+      <c r="S51" s="27"/>
+      <c r="T51" s="27"/>
+      <c r="U51" s="27"/>
+      <c r="V51" s="27"/>
+    </row>
+    <row r="52" spans="17:22" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="Q52" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="R52" s="26"/>
+      <c r="S52" s="26"/>
+      <c r="T52" s="26"/>
+      <c r="U52" s="26"/>
+      <c r="V52" s="26"/>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="24">
+    <mergeCell ref="Q52:V52"/>
     <mergeCell ref="B42:AK42"/>
+    <mergeCell ref="Q48:V48"/>
+    <mergeCell ref="Q49:V49"/>
+    <mergeCell ref="Q50:V50"/>
+    <mergeCell ref="Q51:V51"/>
     <mergeCell ref="E40:G41"/>
     <mergeCell ref="K41:M41"/>
     <mergeCell ref="AF41:AH41"/>
